--- a/frontend/public/templates/internship-portal-people-import-template.xlsx
+++ b/frontend/public/templates/internship-portal-people-import-template.xlsx
@@ -8,9 +8,9 @@
     <sheet name="Field reference" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'People import'!A1:J2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Examples - do not upload'!A1:J9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Field reference'!A1:C12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'People import'!A1:K2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Examples - do not upload'!A1:K9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Field reference'!A1:C13</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -415,7 +415,8 @@
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="22.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,20 +448,23 @@
         <v>batch_year</v>
       </c>
       <c r="J1" t="str">
+        <v>cgpa</v>
+      </c>
+      <c r="K1" t="str">
         <v>mentorship_scope</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:K2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -471,7 +475,8 @@
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="22.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,6 +508,9 @@
         <v>batch_year</v>
       </c>
       <c r="J1" t="str">
+        <v>cgpa</v>
+      </c>
+      <c r="K1" t="str">
         <v>mentorship_scope</v>
       </c>
     </row>
@@ -535,6 +543,9 @@
         <v>2026</v>
       </c>
       <c r="J2" t="str">
+        <v>8.25</v>
+      </c>
+      <c r="K2" t="str">
         <v/>
       </c>
     </row>
@@ -567,6 +578,9 @@
         <v/>
       </c>
       <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>research</v>
       </c>
     </row>
@@ -599,6 +613,9 @@
         <v/>
       </c>
       <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>crcs_self</v>
       </c>
     </row>
@@ -633,6 +650,9 @@
       <c r="J5" t="str">
         <v/>
       </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -665,6 +685,9 @@
       <c r="J6" t="str">
         <v/>
       </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -697,6 +720,9 @@
       <c r="J7" t="str">
         <v/>
       </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -729,6 +755,9 @@
       <c r="J8" t="str">
         <v/>
       </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -761,18 +790,21 @@
       <c r="J9" t="str">
         <v/>
       </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:K9"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -891,30 +923,41 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>mentorship_scope</v>
+        <v>cgpa</v>
       </c>
       <c r="B11" t="str">
-        <v>Faculty/coordinator only</v>
+        <v>Student only</v>
       </c>
       <c r="C11" t="str">
-        <v>research or crcs_self. Leave blank for other roles.</v>
+        <v>Required decimal value from 0 to 10.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>mentorship_scope</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>Faculty/coordinator only</v>
       </c>
       <c r="C12" t="str">
+        <v>research or crcs_self. Leave blank for other roles.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
         <v>The importer reads only the first “People import” sheet. Delete its blank rows only if desired; do not rename its header row.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12"/>
+  <autoFilter ref="A1:C13"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/public/templates/internship-portal-people-import-template.xlsx
+++ b/frontend/public/templates/internship-portal-people-import-template.xlsx
@@ -929,7 +929,7 @@
         <v>Student only</v>
       </c>
       <c r="C11" t="str">
-        <v>Required decimal value from 0 to 10.</v>
+        <v>Optional decimal value from 0 to 10. If blank, bulk upload assigns a random valid value from 6.00 to 10.00.</v>
       </c>
     </row>
     <row r="12">

--- a/frontend/public/templates/internship-portal-people-import-template.xlsx
+++ b/frontend/public/templates/internship-portal-people-import-template.xlsx
@@ -404,20 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:N1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -453,31 +440,26 @@
       <c r="K1" t="str">
         <v>mentorship_scope</v>
       </c>
+      <c r="L1" t="str">
+        <v>additional_role</v>
+      </c>
+      <c r="M1" t="str">
+        <v>additional_role_department_code</v>
+      </c>
+      <c r="N1" t="str">
+        <v>additional_role_school_code</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:N9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -513,6 +495,15 @@
       <c r="K1" t="str">
         <v>mentorship_scope</v>
       </c>
+      <c r="L1" t="str">
+        <v>additional_role</v>
+      </c>
+      <c r="M1" t="str">
+        <v>additional_role_department_code</v>
+      </c>
+      <c r="N1" t="str">
+        <v>additional_role_school_code</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -548,6 +539,15 @@
       <c r="K2" t="str">
         <v/>
       </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -583,6 +583,15 @@
       <c r="K3" t="str">
         <v>research</v>
       </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -618,6 +627,15 @@
       <c r="K4" t="str">
         <v>crcs_self</v>
       </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -653,6 +671,15 @@
       <c r="K5" t="str">
         <v/>
       </c>
+      <c r="L5" t="str">
+        <v>faculty</v>
+      </c>
+      <c r="M5" t="str">
+        <v>CSE</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -688,6 +715,15 @@
       <c r="K6" t="str">
         <v/>
       </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -723,6 +759,15 @@
       <c r="K7" t="str">
         <v/>
       </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -758,6 +803,15 @@
       <c r="K8" t="str">
         <v/>
       </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -793,23 +847,26 @@
       <c r="K9" t="str">
         <v/>
       </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" customWidth="1"/>
-    <col min="3" max="3" width="100.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -945,19 +1002,51 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>additional_role</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="C13" t="str">
+        <v>Optional second role for this person, e.g. an HOD who is also a Faculty Mentor. Same allowed values as role; must differ from role.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>additional_role_department_code</v>
+      </c>
+      <c r="B14" t="str">
+        <v>If additional_role needs a department</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Department code for the additional role (student/faculty/faculty_coordinator/hod).</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>additional_role_school_code</v>
+      </c>
+      <c r="B15" t="str">
+        <v>If additional_role needs a school</v>
+      </c>
+      <c r="C15" t="str">
+        <v>School code for the additional role (dean/school_office).</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
         <v>The importer reads only the first “People import” sheet. Delete its blank rows only if desired; do not rename its header row.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/public/templates/internship-portal-people-import-template.xlsx
+++ b/frontend/public/templates/internship-portal-people-import-template.xlsx
@@ -8,9 +8,9 @@
     <sheet name="Field reference" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'People import'!A1:K2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Examples - do not upload'!A1:K9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Field reference'!A1:C13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'People import'!A1:P2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Examples - do not upload'!A1:P9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Field reference'!A1:C18</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -404,7 +404,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:P1"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
+    <col min="15" max="15" width="30.83203125" customWidth="1"/>
+    <col min="16" max="16" width="26.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -438,28 +456,53 @@
         <v>cgpa</v>
       </c>
       <c r="K1" t="str">
+        <v>program_level</v>
+      </c>
+      <c r="L1" t="str">
+        <v>programme_name</v>
+      </c>
+      <c r="M1" t="str">
         <v>mentorship_scope</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>additional_role</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>additional_role_department_code</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>additional_role_school_code</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:P9"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
+    <col min="15" max="15" width="30.83203125" customWidth="1"/>
+    <col min="16" max="16" width="26.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,15 +536,21 @@
         <v>cgpa</v>
       </c>
       <c r="K1" t="str">
+        <v>program_level</v>
+      </c>
+      <c r="L1" t="str">
+        <v>programme_name</v>
+      </c>
+      <c r="M1" t="str">
         <v>mentorship_scope</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>additional_role</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>additional_role_department_code</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>additional_role_school_code</v>
       </c>
     </row>
@@ -537,15 +586,21 @@
         <v>8.25</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>UG</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>B.Tech</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v/>
       </c>
     </row>
@@ -581,15 +636,21 @@
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>research</v>
       </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v/>
       </c>
     </row>
@@ -625,15 +686,21 @@
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>crcs_self</v>
       </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v/>
       </c>
     </row>
@@ -672,12 +739,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
         <v>faculty</v>
       </c>
-      <c r="M5" t="str">
+      <c r="O5" t="str">
         <v>CSE</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v/>
       </c>
     </row>
@@ -724,6 +797,12 @@
       <c r="N6" t="str">
         <v/>
       </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -768,6 +847,12 @@
       <c r="N7" t="str">
         <v/>
       </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -812,6 +897,12 @@
       <c r="N8" t="str">
         <v/>
       </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -856,17 +947,29 @@
       <c r="N9" t="str">
         <v/>
       </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P9"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="100.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -991,62 +1094,85 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>mentorship_scope</v>
+        <v>program_level</v>
       </c>
       <c r="B12" t="str">
-        <v>Faculty/coordinator only</v>
+        <v>Student only — required</v>
       </c>
       <c r="C12" t="str">
-        <v>research or crcs_self. Leave blank for other roles.</v>
+        <v>UG or PG.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>additional_role</v>
+        <v>programme_name</v>
       </c>
       <c r="B13" t="str">
-        <v>No</v>
+        <v>Student only — optional</v>
       </c>
       <c r="C13" t="str">
-        <v>Optional second role for this person, e.g. an HOD who is also a Faculty Mentor. Same allowed values as role; must differ from role.</v>
+        <v>For example B.Tech, M.Tech, BBA, MBA. Used for department-wise placement reporting when supplied.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>additional_role_department_code</v>
+        <v>mentorship_scope</v>
       </c>
       <c r="B14" t="str">
-        <v>If additional_role needs a department</v>
+        <v>Faculty/coordinator only</v>
       </c>
       <c r="C14" t="str">
-        <v>Department code for the additional role (student/faculty/faculty_coordinator/hod).</v>
+        <v>research or crcs_self. Leave blank for other roles.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>additional_role_school_code</v>
+        <v>additional_role</v>
       </c>
       <c r="B15" t="str">
-        <v>If additional_role needs a school</v>
+        <v>No</v>
       </c>
       <c r="C15" t="str">
-        <v>School code for the additional role (dean/school_office).</v>
+        <v>Give this same row a second role, e.g. a Faculty Mentor who is also a Faculty Coordinator.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>additional_role_department_code</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>Only if additional_role needs a department</v>
       </c>
       <c r="C16" t="str">
+        <v>Must exactly match an existing department code.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>additional_role_school_code</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Only if additional_role needs a school</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Must exactly match an existing school code.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
         <v>The importer reads only the first “People import” sheet. Delete its blank rows only if desired; do not rename its header row.</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C18"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>